--- a/mapping_engine/output/results/nist_rmf__owasp_agentic.xlsx
+++ b/mapping_engine/output/results/nist_rmf__owasp_agentic.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-07T17:32:59.508861+00:00</t>
+          <t>2026-04-08T12:30:11.344401+00:00</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
